--- a/artfynd/A 19748-2024 artfynd.xlsx
+++ b/artfynd/A 19748-2024 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>112353789</v>
       </c>
       <c r="B5" t="n">
-        <v>91971</v>
+        <v>91981</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 19748-2024 artfynd.xlsx
+++ b/artfynd/A 19748-2024 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>112353789</v>
       </c>
       <c r="B5" t="n">
-        <v>91981</v>
+        <v>91993</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 19748-2024 artfynd.xlsx
+++ b/artfynd/A 19748-2024 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>112353789</v>
       </c>
       <c r="B5" t="n">
-        <v>91993</v>
+        <v>91994</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 19748-2024 artfynd.xlsx
+++ b/artfynd/A 19748-2024 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>112353789</v>
       </c>
       <c r="B5" t="n">
-        <v>91994</v>
+        <v>91997</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 19748-2024 artfynd.xlsx
+++ b/artfynd/A 19748-2024 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>112353789</v>
       </c>
       <c r="B5" t="n">
-        <v>91997</v>
+        <v>92003</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 19748-2024 artfynd.xlsx
+++ b/artfynd/A 19748-2024 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>112353789</v>
       </c>
       <c r="B5" t="n">
-        <v>92003</v>
+        <v>92004</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
